--- a/製造チームエビデンス/06_開発時メモ/要件ごとの画面キャプチャ.xlsx
+++ b/製造チームエビデンス/06_開発時メモ/要件ごとの画面キャプチャ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_0F143C0E8B6A5C16837DC052CFD198182C73FA1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{351C68A7-80A5-4F9F-8FEA-B596B3055180}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_793CFF28052AD008E35DD9309F15A7EC2C73FA1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{148CC6E9-9C02-4CF1-B319-9186F14FE22A}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20261009" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,12 +34,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>タスク一覧画面</t>
+    <t>ベース</t>
   </si>
   <si>
-    <t>タスク登録画面</t>
+    <t>ダッシュボード画面</t>
+  </si>
+  <si>
+    <t>タスク追加画面</t>
+  </si>
+  <si>
+    <t>タスク詳細</t>
+  </si>
+  <si>
+    <t>AIアシスタント</t>
+  </si>
+  <si>
+    <t>ダッシュボード分析</t>
   </si>
 </sst>
 </file>
@@ -100,21 +112,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F589AE4-F262-7627-22CD-852C595E6FFB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{624D2BFA-EFC1-77A2-FE76-20C495053FDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -130,8 +142,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="342900"/>
-          <a:ext cx="4572000" cy="2476500"/>
+          <a:off x="0" y="171450"/>
+          <a:ext cx="4572000" cy="2362200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -144,24 +156,24 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8690FBC7-263E-96E4-E872-6E17C7AABCBA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DB07ACE-6767-DE0C-996D-8842983C7FE0}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8F589AE4-F262-7627-22CD-852C595E6FFB}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{624D2BFA-EFC1-77A2-FE76-20C495053FDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -177,8 +189,290 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3429000"/>
-          <a:ext cx="4572000" cy="2466975"/>
+          <a:off x="0" y="2914650"/>
+          <a:ext cx="4572000" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A4DFAB-609C-B82A-26E6-E72EBD21703A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6DB07ACE-6767-DE0C-996D-8842983C7FE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5829300"/>
+          <a:ext cx="4572000" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6A1331A-22BA-F468-FE71-0335C853693A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{95A4DFAB-609C-B82A-26E6-E72EBD21703A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="361950"/>
+          <a:ext cx="4572000" cy="2143125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58C48956-1B7A-4D46-BEA9-44F2CE4D1B9C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7E96D5AF-6E45-B904-D85B-4957679B4233}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="11487150"/>
+          <a:ext cx="4572000" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{702E4327-48F8-42C7-B5C0-F06AFD842D75}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{58C48956-1B7A-4D46-BEA9-44F2CE4D1B9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14401800"/>
+          <a:ext cx="4572000" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{833426AC-97DC-953E-2A74-434CAEE50557}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{702E4327-48F8-42C7-B5C0-F06AFD842D75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="17487900"/>
+          <a:ext cx="4572000" cy="2571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA7E2309-DDC5-7EF7-E9A0-BE94393F5D4A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{833426AC-97DC-953E-2A74-434CAEE50557}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20574000"/>
+          <a:ext cx="4572000" cy="2571750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -487,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:A20"/>
+  <dimension ref="A2:A120"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="2" spans="1:1">
@@ -495,9 +789,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -507,12 +821,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -672,19 +983,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FC6B061-CDF3-4328-9D46-0B2116E478C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4AC08D1-C774-4860-8D58-726919175F9E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08805997-B68B-439F-84D8-F12B78915029}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36856366-1A9A-4D53-A483-622C24721DB1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5A8F31F-7CA5-4837-BA1B-63C862A3516A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC1BAD3B-3DCC-47C0-8260-79B6E28DE34A}"/>
 </file>